--- a/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0002T0006Z000C1N29_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0002T0006Z000C1N29_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>2.665635961935378</v>
+        <v>0.433165843814499</v>
       </c>
       <c r="D2" t="n">
-        <v>23.71708245126284</v>
+        <v>3.854025898330212</v>
       </c>
       <c r="E2" t="n">
-        <v>16.10620884534542</v>
+        <v>2.617258937368632</v>
       </c>
       <c r="F2" t="n">
-        <v>9.639625622746285</v>
+        <v>1.566439163696272</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>10.92673499210748</v>
+        <v>1.775594436217465</v>
       </c>
       <c r="D3" t="n">
-        <v>15.52417469626002</v>
+        <v>2.522678388142254</v>
       </c>
       <c r="E3" t="n">
-        <v>16.10620884534542</v>
+        <v>2.617258937368632</v>
       </c>
       <c r="F3" t="n">
-        <v>9.639625622746285</v>
+        <v>1.566439163696272</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>20.45734867995704</v>
+        <v>3.324319160493019</v>
       </c>
       <c r="D4" t="n">
-        <v>19.21235154098153</v>
+        <v>3.122007125409499</v>
       </c>
       <c r="E4" t="n">
-        <v>16.10620884534542</v>
+        <v>2.617258937368632</v>
       </c>
       <c r="F4" t="n">
-        <v>9.639625622746285</v>
+        <v>1.566439163696272</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>27.71837566217073</v>
+        <v>4.504236045102743</v>
       </c>
       <c r="D5" t="n">
-        <v>10.73545527679194</v>
+        <v>1.744511482478691</v>
       </c>
       <c r="E5" t="n">
-        <v>16.10620884534542</v>
+        <v>2.617258937368632</v>
       </c>
       <c r="F5" t="n">
-        <v>9.639625622746285</v>
+        <v>1.566439163696272</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>26.95699802628474</v>
+        <v>4.380512179271271</v>
       </c>
       <c r="D6" t="n">
-        <v>27.18915224864505</v>
+        <v>4.41823724040482</v>
       </c>
       <c r="E6" t="n">
-        <v>16.10620884534542</v>
+        <v>2.617258937368632</v>
       </c>
       <c r="F6" t="n">
-        <v>9.639625622746285</v>
+        <v>1.566439163696272</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>37.28664738242574</v>
+        <v>6.059080199644183</v>
       </c>
       <c r="D7" t="n">
-        <v>14.08556062320465</v>
+        <v>2.288903601270756</v>
       </c>
       <c r="E7" t="n">
-        <v>16.10620884534542</v>
+        <v>2.617258937368632</v>
       </c>
       <c r="F7" t="n">
-        <v>9.639625622746285</v>
+        <v>1.566439163696272</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>44.77683242984189</v>
+        <v>7.276235269849307</v>
       </c>
       <c r="D8" t="n">
-        <v>23.09622188234247</v>
+        <v>3.753136055880652</v>
       </c>
       <c r="E8" t="n">
-        <v>16.10620884534542</v>
+        <v>2.617258937368632</v>
       </c>
       <c r="F8" t="n">
-        <v>9.639625622746285</v>
+        <v>1.566439163696272</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>45.11897369296917</v>
+        <v>7.33183322510749</v>
       </c>
       <c r="D9" t="n">
-        <v>27.3230553338989</v>
+        <v>4.439996491758572</v>
       </c>
       <c r="E9" t="n">
-        <v>16.10620884534542</v>
+        <v>2.617258937368632</v>
       </c>
       <c r="F9" t="n">
-        <v>9.639625622746285</v>
+        <v>1.566439163696272</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>24.98119774148355</v>
+        <v>4.059444632991077</v>
       </c>
       <c r="D10" t="n">
-        <v>9.257051884667051</v>
+        <v>1.504270931258396</v>
       </c>
       <c r="E10" t="n">
-        <v>16.10620884534542</v>
+        <v>2.617258937368632</v>
       </c>
       <c r="F10" t="n">
-        <v>9.639625622746285</v>
+        <v>1.566439163696272</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>9.881285335365472</v>
+        <v>1.605708866996889</v>
       </c>
       <c r="D11" t="n">
-        <v>13.81433578577083</v>
+        <v>2.244829565187759</v>
       </c>
       <c r="E11" t="n">
-        <v>16.10620884534542</v>
+        <v>2.617258937368632</v>
       </c>
       <c r="F11" t="n">
-        <v>9.639625622746285</v>
+        <v>1.566439163696272</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>63.28400674892936</v>
+        <v>10.28365109670102</v>
       </c>
       <c r="D12" t="n">
-        <v>25.27893406654601</v>
+        <v>4.107826785813727</v>
       </c>
       <c r="E12" t="n">
-        <v>16.10620884534542</v>
+        <v>2.617258937368632</v>
       </c>
       <c r="F12" t="n">
-        <v>9.639625622746285</v>
+        <v>1.566439163696272</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>25.43028708510684</v>
+        <v>4.132421651329862</v>
       </c>
       <c r="D13" t="n">
-        <v>37.42930370089103</v>
+        <v>6.082261851394792</v>
       </c>
       <c r="E13" t="n">
-        <v>16.10620884534542</v>
+        <v>2.617258937368632</v>
       </c>
       <c r="F13" t="n">
-        <v>9.639625622746285</v>
+        <v>1.566439163696272</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>40.25891560255724</v>
+        <v>6.542073785415552</v>
       </c>
       <c r="D14" t="n">
-        <v>42.78593889096068</v>
+        <v>6.95271506978111</v>
       </c>
       <c r="E14" t="n">
-        <v>16.10620884534542</v>
+        <v>2.617258937368632</v>
       </c>
       <c r="F14" t="n">
-        <v>9.639625622746285</v>
+        <v>1.566439163696272</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
